--- a/dataset_t6_grouped/results2/G1/G1_T1912_W0046F0002T0006Z000C1N22_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G1/G1_T1912_W0046F0002T0006Z000C1N22_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>16.63623667106121</v>
+        <v>2.703388459047447</v>
       </c>
       <c r="D2" t="n">
-        <v>6.24346022734391</v>
+        <v>1.014562286943385</v>
       </c>
       <c r="E2" t="n">
-        <v>8.808124429683218</v>
+        <v>1.431320219823523</v>
       </c>
       <c r="F2" t="n">
-        <v>11.53268535223324</v>
+        <v>1.874061369737902</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>34.33127434352601</v>
+        <v>5.578832080822977</v>
       </c>
       <c r="D3" t="n">
-        <v>20.67415312554954</v>
+        <v>3.3595498829018</v>
       </c>
       <c r="E3" t="n">
-        <v>8.808124429683218</v>
+        <v>1.431320219823523</v>
       </c>
       <c r="F3" t="n">
-        <v>11.53268535223324</v>
+        <v>1.874061369737902</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>34.78499445210674</v>
+        <v>5.652561598467346</v>
       </c>
       <c r="D4" t="n">
-        <v>35.35645796203687</v>
+        <v>5.745424418830992</v>
       </c>
       <c r="E4" t="n">
-        <v>8.808124429683218</v>
+        <v>1.431320219823523</v>
       </c>
       <c r="F4" t="n">
-        <v>11.53268535223324</v>
+        <v>1.874061369737902</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>25.24472956946651</v>
+        <v>4.102268555038309</v>
       </c>
       <c r="D5" t="n">
-        <v>3.65752569695724</v>
+        <v>0.5943479257555515</v>
       </c>
       <c r="E5" t="n">
-        <v>8.808124429683218</v>
+        <v>1.431320219823523</v>
       </c>
       <c r="F5" t="n">
-        <v>11.53268535223324</v>
+        <v>1.874061369737902</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>13.3740327804949</v>
+        <v>2.173280326830421</v>
       </c>
       <c r="D6" t="n">
-        <v>11.25078550847492</v>
+        <v>1.828252645127175</v>
       </c>
       <c r="E6" t="n">
-        <v>8.808124429683218</v>
+        <v>1.431320219823523</v>
       </c>
       <c r="F6" t="n">
-        <v>11.53268535223324</v>
+        <v>1.874061369737902</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
